--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.754465307740046</v>
+        <v>1.097600612507758</v>
       </c>
       <c r="D2" t="n">
-        <v>6.562414467606436</v>
+        <v>1.066392350986046</v>
       </c>
       <c r="E2" t="n">
-        <v>5.85597830751311</v>
+        <v>0.9515964749708804</v>
       </c>
       <c r="F2" t="n">
-        <v>6.176156988217971</v>
+        <v>1.003625510585421</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.46642192276627</v>
+        <v>3.000793562449518</v>
       </c>
       <c r="D3" t="n">
-        <v>18.91472844404238</v>
+        <v>3.073643372156887</v>
       </c>
       <c r="E3" t="n">
-        <v>5.85597830751311</v>
+        <v>0.9515964749708804</v>
       </c>
       <c r="F3" t="n">
-        <v>6.176156988217971</v>
+        <v>1.003625510585421</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
